--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:34:08+00:00</t>
+    <t>2026-04-15T07:49:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:49:49+00:00</t>
+    <t>2026-04-16T07:52:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-demande-d-examen-ou-de-suivi.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$90</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2504" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2853" uniqueCount="330">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -571,6 +571,132 @@
     <t>http://terminology.hl7.org/ValueSet/v3-ObservationType</t>
   </si>
   <si>
+    <t>Observation.code.nullFlavor</t>
+  </si>
+  <si>
+    <t>Observation.code.code</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
+</t>
+  </si>
+  <si>
+    <t>The text or phrase used as the basis for the coding.</t>
+  </si>
+  <si>
+    <t>CD.originalText</t>
+  </si>
+  <si>
+    <t>Observation.code.qualifier</t>
+  </si>
+  <si>
+    <t>Qualifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
+</t>
+  </si>
+  <si>
+    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
+  </si>
+  <si>
+    <t>CD.qualifier</t>
+  </si>
+  <si>
+    <t>Observation.code.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
+  </si>
+  <si>
     <t>Observation.derivationExpr</t>
   </si>
   <si>
@@ -579,10 +705,6 @@
   </si>
   <si>
     <t>Observation.text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
-</t>
   </si>
   <si>
     <t>Description narrative</t>
@@ -1245,7 +1367,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK79"/>
+  <dimension ref="A1:AK90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="70.34765625" customWidth="true" bestFit="true"/>
@@ -4568,7 +4690,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>168</v>
       </c>
@@ -4587,7 +4709,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
@@ -4882,7 +5004,9 @@
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E36" s="2"/>
+      <c r="E36" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
@@ -4899,10 +5023,12 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>178</v>
+        <v>85</v>
       </c>
       <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
+      <c r="M36" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -4928,13 +5054,11 @@
         <v>74</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>74</v>
@@ -4952,7 +5076,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>177</v>
+        <v>89</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4972,16 +5096,18 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E37" s="2"/>
+      <c r="E37" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F37" t="s" s="2">
         <v>75</v>
       </c>
@@ -4998,12 +5124,12 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="M37" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="L37" s="2"/>
+      <c r="M37" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5053,7 +5179,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5071,28 +5197,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>84</v>
+        <v>182</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>74</v>
@@ -5101,11 +5227,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>86</v>
+        <v>183</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5132,11 +5258,13 @@
         <v>74</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>74</v>
@@ -5154,7 +5282,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5174,17 +5302,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5202,11 +5330,11 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5233,11 +5361,13 @@
         <v>74</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>186</v>
+        <v>74</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>74</v>
@@ -5255,7 +5385,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5275,17 +5405,17 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>80</v>
@@ -5303,7 +5433,7 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>190</v>
+        <v>102</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
@@ -5376,7 +5506,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>193</v>
       </c>
@@ -5397,7 +5527,7 @@
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -5406,7 +5536,7 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
@@ -5437,29 +5567,31 @@
         <v>74</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y41" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5479,18 +5611,16 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E42" t="s" s="2">
-        <v>199</v>
-      </c>
+      <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
@@ -5507,11 +5637,11 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5562,7 +5692,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5582,18 +5712,16 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E43" t="s" s="2">
-        <v>203</v>
-      </c>
+      <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
@@ -5610,11 +5738,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5641,11 +5769,13 @@
         <v>74</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>205</v>
+        <v>74</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>74</v>
@@ -5663,7 +5793,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5683,16 +5813,18 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E44" s="2"/>
+      <c r="E44" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
@@ -5709,10 +5841,12 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="L44" s="2"/>
-      <c r="M44" s="2"/>
+      <c r="M44" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -5738,29 +5872,31 @@
         <v>74</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5780,21 +5916,23 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E45" s="2"/>
+      <c r="E45" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>74</v>
@@ -5806,17 +5944,13 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L45" t="s" s="2">
         <v>211</v>
       </c>
+      <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="N45" t="s" s="2">
-        <v>213</v>
-      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>74</v>
@@ -5865,13 +5999,13 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>74</v>
@@ -5885,41 +6019,39 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E46" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="F46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L46" s="2"/>
+      <c r="M46" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="F46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5970,13 +6102,13 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>74</v>
@@ -5990,18 +6122,16 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E47" t="s" s="2">
-        <v>222</v>
-      </c>
+      <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
@@ -6018,12 +6148,10 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="L47" s="2"/>
-      <c r="M47" t="s" s="2">
-        <v>223</v>
-      </c>
+      <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6073,7 +6201,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6093,10 +6221,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6119,14 +6247,12 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>91</v>
+        <v>206</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6152,11 +6278,13 @@
         <v>74</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y48" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z48" t="s" s="2">
-        <v>227</v>
+        <v>74</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>74</v>
@@ -6174,7 +6302,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6192,26 +6320,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E49" s="2"/>
+      <c r="E49" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F49" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>74</v>
@@ -6220,13 +6350,11 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>231</v>
+        <v>86</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6253,13 +6381,11 @@
         <v>74</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>74</v>
@@ -6277,7 +6403,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>228</v>
+        <v>89</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6297,16 +6423,18 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E50" s="2"/>
+      <c r="E50" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
@@ -6323,10 +6451,12 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>233</v>
+        <v>85</v>
       </c>
       <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
+      <c r="M50" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -6352,11 +6482,11 @@
         <v>74</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>175</v>
+        <v>87</v>
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>74</v>
@@ -6374,7 +6504,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6394,16 +6524,18 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E51" s="2"/>
+      <c r="E51" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
@@ -6420,10 +6552,12 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="L51" s="2"/>
-      <c r="M51" s="2"/>
+      <c r="M51" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -6473,7 +6607,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6493,16 +6627,18 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E52" s="2"/>
+      <c r="E52" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
@@ -6519,10 +6655,12 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
+      <c r="M52" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -6552,7 +6690,7 @@
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>74</v>
@@ -6588,18 +6726,20 @@
         <v>74</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E53" s="2"/>
+      <c r="E53" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
@@ -6607,7 +6747,7 @@
         <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -6616,12 +6756,12 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L53" s="2"/>
+      <c r="M53" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="L53" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="M53" s="2"/>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -6671,13 +6811,13 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>74</v>
@@ -6689,7 +6829,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>242</v>
       </c>
@@ -6700,7 +6840,9 @@
       <c r="D54" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E54" s="2"/>
+      <c r="E54" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
@@ -6708,7 +6850,7 @@
         <v>75</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>74</v>
@@ -6717,13 +6859,11 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6750,11 +6890,11 @@
         <v>74</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>87</v>
+        <v>175</v>
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>74</v>
@@ -6772,13 +6912,13 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>74</v>
@@ -6790,12 +6930,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6809,7 +6949,7 @@
         <v>75</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>74</v>
@@ -6818,14 +6958,10 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -6851,11 +6987,11 @@
         <v>74</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>175</v>
+        <v>87</v>
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>74</v>
@@ -6873,13 +7009,13 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>74</v>
@@ -6893,10 +7029,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6907,7 +7043,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>74</v>
@@ -6919,15 +7055,17 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>171</v>
+        <v>102</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>74</v>
@@ -6976,13 +7114,13 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>74</v>
@@ -6996,18 +7134,20 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E57" s="2"/>
+      <c r="E57" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>75</v>
@@ -7022,10 +7162,14 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="L57" s="2"/>
-      <c r="M57" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7075,7 +7219,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7095,21 +7239,23 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E58" s="2"/>
+      <c r="E58" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>74</v>
@@ -7121,10 +7267,12 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>253</v>
+        <v>206</v>
       </c>
       <c r="L58" s="2"/>
-      <c r="M58" s="2"/>
+      <c r="M58" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7174,13 +7322,13 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>74</v>
@@ -7192,12 +7340,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7205,13 +7353,13 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>74</v>
@@ -7220,10 +7368,14 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="L59" s="2"/>
-      <c r="M59" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -7249,13 +7401,11 @@
         <v>74</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>74</v>
+        <v>267</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7273,13 +7423,13 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>74</v>
@@ -7291,12 +7441,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7304,13 +7454,13 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>74</v>
@@ -7319,13 +7469,13 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7376,13 +7526,13 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>74</v>
@@ -7396,10 +7546,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7410,7 +7560,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>74</v>
@@ -7422,7 +7572,7 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -7451,13 +7601,11 @@
         <v>74</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>74</v>
+        <v>274</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>74</v>
@@ -7475,13 +7623,13 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>74</v>
@@ -7495,10 +7643,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7509,7 +7657,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>74</v>
@@ -7521,7 +7669,7 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -7574,13 +7722,13 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>74</v>
@@ -7594,10 +7742,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7608,7 +7756,7 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>74</v>
@@ -7620,7 +7768,7 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>264</v>
+        <v>91</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -7649,13 +7797,11 @@
         <v>74</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>74</v>
+        <v>278</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>74</v>
@@ -7673,13 +7819,13 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>74</v>
@@ -7691,12 +7837,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7707,10 +7853,10 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>74</v>
@@ -7719,9 +7865,11 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="L64" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7772,7 +7920,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7790,12 +7938,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7806,10 +7954,10 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>74</v>
@@ -7818,10 +7966,14 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="L65" s="2"/>
-      <c r="M65" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -7847,13 +7999,11 @@
         <v>74</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>74</v>
+        <v>284</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>74</v>
@@ -7871,7 +8021,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -7889,12 +8039,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -7905,10 +8055,10 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>74</v>
@@ -7917,10 +8067,14 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="L66" s="2"/>
-      <c r="M66" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -7946,13 +8100,11 @@
         <v>74</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>74</v>
+        <v>287</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>74</v>
@@ -7970,7 +8122,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -7990,10 +8142,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8016,11 +8168,13 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="L67" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="M67" t="s" s="2">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8071,7 +8225,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8091,18 +8245,16 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E68" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
@@ -8119,12 +8271,10 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>85</v>
+        <v>291</v>
       </c>
       <c r="L68" s="2"/>
-      <c r="M68" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M68" s="2"/>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -8150,11 +8300,13 @@
         <v>74</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y68" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z68" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>74</v>
@@ -8172,7 +8324,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>89</v>
+        <v>290</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8192,10 +8344,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8218,12 +8370,10 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>91</v>
+        <v>293</v>
       </c>
       <c r="L69" s="2"/>
-      <c r="M69" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M69" s="2"/>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -8273,7 +8423,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>93</v>
+        <v>292</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8293,10 +8443,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8307,7 +8457,7 @@
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>74</v>
@@ -8319,12 +8469,10 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>95</v>
+        <v>295</v>
       </c>
       <c r="L70" s="2"/>
-      <c r="M70" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M70" s="2"/>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -8374,19 +8522,19 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>97</v>
+        <v>294</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>74</v>
@@ -8394,23 +8542,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E71" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>74</v>
@@ -8422,11 +8568,13 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L71" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="M71" t="s" s="2">
-        <v>86</v>
+        <v>298</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8453,11 +8601,13 @@
         <v>74</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y71" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z71" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>74</v>
@@ -8475,13 +8625,13 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>89</v>
+        <v>296</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>74</v>
@@ -8495,23 +8645,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E72" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>74</v>
@@ -8523,12 +8671,10 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>102</v>
+        <v>300</v>
       </c>
       <c r="L72" s="2"/>
-      <c r="M72" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M72" s="2"/>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -8578,13 +8724,13 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>104</v>
+        <v>299</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>74</v>
@@ -8598,23 +8744,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E73" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>74</v>
@@ -8626,12 +8770,10 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>107</v>
+        <v>302</v>
       </c>
       <c r="L73" s="2"/>
-      <c r="M73" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M73" s="2"/>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -8681,13 +8823,13 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>109</v>
+        <v>301</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>74</v>
@@ -8701,23 +8843,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E74" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>74</v>
@@ -8729,12 +8869,10 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>112</v>
+        <v>304</v>
       </c>
       <c r="L74" s="2"/>
-      <c r="M74" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M74" s="2"/>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -8742,7 +8880,7 @@
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>74</v>
@@ -8784,13 +8922,13 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>115</v>
+        <v>303</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>74</v>
@@ -8804,23 +8942,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E75" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>74</v>
@@ -8832,12 +8968,10 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>102</v>
+        <v>306</v>
       </c>
       <c r="L75" s="2"/>
-      <c r="M75" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M75" s="2"/>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -8887,13 +9021,13 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>119</v>
+        <v>305</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>74</v>
@@ -8907,10 +9041,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -8933,12 +9067,10 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>95</v>
+        <v>308</v>
       </c>
       <c r="L76" s="2"/>
-      <c r="M76" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M76" s="2"/>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -8988,7 +9120,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>125</v>
+        <v>307</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9008,10 +9140,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>283</v>
+        <v>309</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>283</v>
+        <v>309</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9022,7 +9154,7 @@
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>74</v>
@@ -9034,7 +9166,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>85</v>
+        <v>310</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9045,7 +9177,7 @@
       </c>
       <c r="Q77" s="2"/>
       <c r="R77" t="s" s="2">
-        <v>284</v>
+        <v>74</v>
       </c>
       <c r="S77" t="s" s="2">
         <v>74</v>
@@ -9063,11 +9195,13 @@
         <v>74</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y77" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z77" t="s" s="2">
-        <v>285</v>
+        <v>74</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>74</v>
@@ -9085,13 +9219,13 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>283</v>
+        <v>309</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>74</v>
@@ -9105,10 +9239,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9116,10 +9250,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>74</v>
@@ -9131,10 +9265,12 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="L78" s="2"/>
-      <c r="M78" s="2"/>
+      <c r="M78" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -9184,13 +9320,13 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>74</v>
@@ -9204,21 +9340,23 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E79" s="2"/>
+      <c r="E79" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>74</v>
@@ -9230,10 +9368,12 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>289</v>
+        <v>85</v>
       </c>
       <c r="L79" s="2"/>
-      <c r="M79" s="2"/>
+      <c r="M79" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -9259,13 +9399,11 @@
         <v>74</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>74</v>
@@ -9283,26 +9421,1137 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>288</v>
+        <v>89</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G80" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK79" t="s" s="2">
+      <c r="H80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L80" s="2"/>
+      <c r="M80" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L81" s="2"/>
+      <c r="M81" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L82" s="2"/>
+      <c r="M82" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y82" s="2"/>
+      <c r="Z82" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E83" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L83" s="2"/>
+      <c r="M83" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E84" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="F84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L84" s="2"/>
+      <c r="M84" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E85" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L85" s="2"/>
+      <c r="M85" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E86" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L86" s="2"/>
+      <c r="M86" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L87" s="2"/>
+      <c r="M87" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L88" s="2"/>
+      <c r="M88" s="2"/>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y88" s="2"/>
+      <c r="Z88" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="L89" s="2"/>
+      <c r="M89" s="2"/>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L90" s="2"/>
+      <c r="M90" s="2"/>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK90" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK79">
+  <autoFilter ref="A1:AK90">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9312,7 +10561,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI78">
+  <conditionalFormatting sqref="A2:AI89">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
